--- a/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,59</t>
+          <t>0,0; 56,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,48</t>
+          <t>0,0; 27,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,42</t>
+          <t>0,0; 32,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 17,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,14</t>
+          <t>0,0; 13,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 31,13</t>
+          <t>4,23; 32,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 30,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,93</t>
+          <t>2,28; 19,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,76</t>
+          <t>1,51; 17,02</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,78</t>
+          <t>0,0; 30,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,77</t>
+          <t>0,0; 32,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,0</t>
+          <t>0,0; 58,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,76</t>
+          <t>0,0; 18,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,47</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,06</t>
+          <t>0,0; 77,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,34</t>
+          <t>0,0; 41,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,59</t>
+          <t>0,0; 28,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,66</t>
+          <t>0,0; 37,53</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,34</t>
+          <t>1,08; 10,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,79</t>
+          <t>1,06; 9,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,37</t>
+          <t>1,38; 11,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,28</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,96</t>
+          <t>1,54; 14,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,0</t>
+          <t>1,53; 8,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,14</t>
+          <t>0,5; 4,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,43</t>
+          <t>1,77; 9,34</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3257</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3939</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3059</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2463</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2806</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>647; 5023</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5202</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>664; 5559</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>565; 6371</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3129</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3153</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5281</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2640</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2637</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2737</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>447; 4364</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4234</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>560; 5172</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>642; 5413</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4646</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>706; 6612</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1346; 7378</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>600; 5399</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1752; 9223</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,63</t>
+          <t>0,0; 52,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,34</t>
+          <t>0,0; 24,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,94</t>
+          <t>0,0; 22,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 19,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,81</t>
+          <t>0,0; 17,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,65</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 32,82</t>
+          <t>4,22; 33,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,82</t>
+          <t>0,0; 29,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 19,08</t>
+          <t>2,2; 19,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 17,02</t>
+          <t>1,53; 15,59</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,46</t>
+          <t>0,0; 28,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,83</t>
+          <t>0,0; 37,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,86</t>
+          <t>0,0; 48,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,45</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,83</t>
+          <t>0,0; 26,11</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,52</t>
+          <t>0,0; 77,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,36</t>
+          <t>0,0; 40,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 35,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,53</t>
+          <t>0,0; 35,34</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,52</t>
+          <t>1,06; 9,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,8</t>
+          <t>1,04; 9,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,59</t>
+          <t>1,38; 10,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,39</t>
+          <t>1,51; 14,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,37</t>
+          <t>1,74; 8,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,53</t>
+          <t>0,51; 4,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,34</t>
+          <t>1,53; 8,99</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>0; 3550</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 2765</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3059</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2463</t>
+          <t>0; 2427</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2806</t>
+          <t>0; 3107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647; 5023</t>
+          <t>645; 5126</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5202</t>
+          <t>0; 5022</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>664; 5559</t>
+          <t>642; 5743</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>565; 6371</t>
+          <t>572; 5835</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3129</t>
+          <t>0; 2907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3153</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4084</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5281</t>
+          <t>0; 4623</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2640</t>
+          <t>0; 2630</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 2619</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2637</t>
+          <t>0; 3278</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2737</t>
+          <t>0; 2577</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>447; 4364</t>
+          <t>438; 4022</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>0; 2750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>560; 5172</t>
+          <t>547; 4811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>642; 5413</t>
+          <t>643; 4849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4646</t>
+          <t>0; 4252</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>706; 6612</t>
+          <t>693; 6878</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1346; 7378</t>
+          <t>1535; 7666</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>600; 5399</t>
+          <t>611; 5564</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1752; 9223</t>
+          <t>1511; 8874</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,02%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 24,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -740,22 +740,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,51%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,64</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,55</t>
+          <t>4,18; 31,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>0,0; 31,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 33,49</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,76</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 19,71</t>
+          <t>2,25; 19,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 15,59</t>
+          <t>1,51; 15,76</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>5,55%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,3</t>
+          <t>0,0; 47,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,44</t>
+          <t>0,0; 23,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 16,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,11</t>
+          <t>0,0; 27,47</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>18,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 78,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,24</t>
+          <t>0,0; 27,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,34</t>
+          <t>0,0; 50,66</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,31%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,7</t>
+          <t>1,38; 10,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 8,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,11</t>
+          <t>1,53; 14,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,38</t>
+          <t>1,08; 10,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,97</t>
+          <t>1,04; 8,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,69</t>
+          <t>1,49; 8,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,66</t>
+          <t>0,51; 5,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,99</t>
+          <t>1,74; 9,43</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,22 +1533,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1094</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3550</t>
+          <t>0; 3527</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1754,22 +1754,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>669</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2765</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3481</t>
+          <t>0; 3577</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>560</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2427</t>
+          <t>639; 4765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3107</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645; 5126</t>
+          <t>0; 1952</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5022</t>
+          <t>0; 2907</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>642; 5743</t>
+          <t>655; 5807</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>572; 5835</t>
+          <t>565; 5899</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>731</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>570</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3051</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2907</t>
+          <t>0; 3493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 2442</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4084</t>
+          <t>0; 3637</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4623</t>
+          <t>0; 4863</t>
         </is>
       </c>
     </row>
@@ -2353,27 +2353,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2406,27 +2406,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2710</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2659</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3278</t>
+          <t>0; 2567</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2577</t>
+          <t>0; 3694</t>
         </is>
       </c>
     </row>
@@ -2516,22 +2516,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1747</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>438; 4022</t>
+          <t>643; 4841</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2750</t>
+          <t>0; 4858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>547; 4811</t>
+          <t>703; 6875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>643; 4849</t>
+          <t>448; 4287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4252</t>
+          <t>0; 3510</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>693; 6878</t>
+          <t>550; 4643</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1535; 7666</t>
+          <t>1315; 7051</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>611; 5564</t>
+          <t>607; 6134</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1511; 8874</t>
+          <t>1716; 9311</t>
         </is>
       </c>
     </row>
